--- a/uploads/excels/baitaranipvt.xlsx
+++ b/uploads/excels/baitaranipvt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5DAE9C-DB9D-4C60-BA3B-FEEFD4B6BFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFF0685-D5D0-41C4-892E-9EB2E30CB0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2473,7 +2473,7 @@
         <v>135</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F5" s="5">
         <v>4</v>
@@ -2739,7 +2739,7 @@
         <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F6" s="5">
         <v>5</v>

--- a/uploads/excels/baitaranipvt.xlsx
+++ b/uploads/excels/baitaranipvt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFF0685-D5D0-41C4-892E-9EB2E30CB0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BD6B89-CBB2-4286-9E8E-B11CC403F946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="262">
   <si>
     <t>chhendipada</t>
   </si>
@@ -807,9 +807,6 @@
   </si>
   <si>
     <t>2836 1246 1278</t>
-  </si>
-  <si>
-    <t>Person Affected Families</t>
   </si>
   <si>
     <t>PAF</t>
@@ -1667,7 +1664,7 @@
         <v>253</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -1937,7 +1934,7 @@
         <v>253</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F3" s="5">
         <v>2</v>
@@ -2473,7 +2470,7 @@
         <v>135</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F5" s="5">
         <v>4</v>
@@ -2739,7 +2736,7 @@
         <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F6" s="5">
         <v>5</v>
